--- a/Table/Table.xlsx
+++ b/Table/Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Sulfate_Drain\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6534B5-7C8C-40BF-9BEA-56748CCC2E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6153465A-FF58-4A8E-AC7E-F62A5FFECE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-3790" windowWidth="38620" windowHeight="21100" xr2:uid="{4026D0F1-A8B9-45FD-A778-6277D8F14AA6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4026D0F1-A8B9-45FD-A778-6277D8F14AA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -813,14 +813,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A8914E-7238-474F-81EE-95EF26EA0AEC}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="22.1328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.06640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.1328125" style="2" customWidth="1"/>
+    <col min="1" max="3" width="22.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -837,7 +837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.649999999999999" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -847,12 +847,14 @@
       <c r="C2" s="3">
         <v>1.698</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3">
+        <v>1078</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,12 +864,14 @@
       <c r="C3" s="3">
         <v>4.4530000000000003</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="3">
+        <v>1453</v>
+      </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.649999999999999" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -877,12 +881,14 @@
       <c r="C4" s="3">
         <v>0.76400000000000001</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3">
+        <v>442</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -892,12 +898,14 @@
       <c r="C5" s="4">
         <v>1.61</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>358</v>
+      </c>
       <c r="E5" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -908,7 +916,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -925,7 +933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -942,7 +950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -959,28 +967,28 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <f>(B2-B5)/B2</f>
         <v>0.97627859276764617</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>21</v>
       </c>

--- a/Table/Table.xlsx
+++ b/Table/Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Documents\GitHub\Sulfate_Drain\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6153465A-FF58-4A8E-AC7E-F62A5FFECE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1578A7E4-89A6-4715-8399-B1CE4539EC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4026D0F1-A8B9-45FD-A778-6277D8F14AA6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{4026D0F1-A8B9-45FD-A778-6277D8F14AA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>Treatment</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Continuous flood with sulfate (CF-S)</t>
   </si>
   <si>
-    <t>Mid-season with sulfate (MD-S)</t>
-  </si>
-  <si>
     <t>Sources of variation</t>
   </si>
   <si>
@@ -152,7 +149,26 @@
   </si>
   <si>
     <r>
-      <t>14.1</t>
+      <t>Global warming potential (kg CO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> eq ha</t>
     </r>
     <r>
       <rPr>
@@ -162,12 +178,89 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>12.9</t>
+      <t>−1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Drain x Sulfate</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-value</t>
+    </r>
+  </si>
+  <si>
+    <t>ns</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> CH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (kg CH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> ha</t>
     </r>
     <r>
       <rPr>
@@ -177,70 +270,6 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>16.6</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>14.8</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Global warming potential (kg CO</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> eq ha</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>−1</t>
     </r>
     <r>
@@ -254,9 +283,12 @@
     </r>
   </si>
   <si>
-    <t>Drain x Sulfate</t>
-  </si>
-  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* </t>
+    </r>
     <r>
       <rPr>
         <i/>
@@ -274,18 +306,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>-value</t>
-    </r>
-  </si>
-  <si>
-    <t>ns</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⁺ p &lt; .10. * p &lt; 0.05. </t>
+      <t xml:space="preserve"> &lt; 0.05. </t>
     </r>
     <r>
       <rPr>
@@ -308,69 +329,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> CH</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (kg CH</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t> ha</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>−1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>Mid-season drain with sulfate (MD-S)</t>
   </si>
 </sst>
 </file>
@@ -457,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -473,6 +432,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -813,31 +775,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A8914E-7238-474F-81EE-95EF26EA0AEC}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="22.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.265625" style="2" customWidth="1"/>
+    <col min="2" max="5" width="15.73046875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="50.65" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -850,11 +811,11 @@
       <c r="D2" s="3">
         <v>1078</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="E2" s="3">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,11 +828,11 @@
       <c r="D3" s="3">
         <v>1453</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E3" s="3">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -884,13 +845,13 @@
       <c r="D4" s="3">
         <v>442</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="E4" s="3">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4">
         <v>0.53200000000000003</v>
@@ -901,96 +862,96 @@
       <c r="D5" s="4">
         <v>358</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="4">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B13" s="3"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B18" s="2">
         <f>(B2-B5)/B2</f>
         <v>0.97627859276764617</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
